--- a/260808.xlsx
+++ b/260808.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525E28A2-1BEA-4958-8538-651BC1E1BEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAFCBE6-A4CB-4390-91C6-2FEC943D68A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10570" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -404,15 +404,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>das sind in der Regel Zeugen, die als Flüchtlinge hierher nach Deutschland gekommen sind –,  die wir vielleicht einmal nutzbar machen können, wenn Teilnehmer solcher Kriegsverbrecherhandlungen hierher nach Deutschland kommen.
-hätten wir dieses Gespräch wahrscheinlich mit dem Schwerpunkt Rechtsextremismus begonnen.
-Sie haben mehrere Verfahren übernommen.
-Im April haben Sie fünf Personen festnehmen lassen wegen des Verdachts der Mitgliedschaft in einer rechtsterroristischen Vereinigung.
-Dieser  Gruppe Freital.
-rechnen Sie auch noch weitere Personen hinzu.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
 Wir wollen den Kanzler dieser Republik stellen.
 Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
@@ -574,6 +565,10 @@
     <t>In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
 Aber dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben.
 Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kriegsverbrecherhandlungen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -905,12 +900,12 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="26.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +924,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +943,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="182" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -991,10 +986,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
